--- a/Methanol/Methanol_DAC_Brownfield_Leuna/Datenbank.xlsx
+++ b/Methanol/Methanol_DAC_Brownfield_Leuna/Datenbank.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Methanol\Methanol_DAC_Brownfield_Patagonien\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Methanol\Methanol_DAC_Brownfield_Leuna\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C86752FF-C744-4DE2-B065-1CB0B0DF3433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52B68AD7-D372-408F-9EB1-6562BD3F2D16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -2983,7 +2983,7 @@
         <v>75</v>
       </c>
       <c r="E54" s="12">
-        <v>0.1173</v>
+        <v>0.1699</v>
       </c>
       <c r="F54" s="11" t="s">
         <v>19</v>
@@ -5222,6 +5222,15 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A2:A43"/>
+    <mergeCell ref="B2:B11"/>
+    <mergeCell ref="B12:B22"/>
+    <mergeCell ref="B33:B43"/>
+    <mergeCell ref="A44:A75"/>
+    <mergeCell ref="B64:B75"/>
+    <mergeCell ref="B23:B32"/>
+    <mergeCell ref="B44:B53"/>
+    <mergeCell ref="B54:B63"/>
     <mergeCell ref="B142:B143"/>
     <mergeCell ref="B136:B141"/>
     <mergeCell ref="A113:A144"/>
@@ -5237,15 +5246,6 @@
     <mergeCell ref="B107:B109"/>
     <mergeCell ref="B99:B102"/>
     <mergeCell ref="B103:B106"/>
-    <mergeCell ref="A2:A43"/>
-    <mergeCell ref="B2:B11"/>
-    <mergeCell ref="B12:B22"/>
-    <mergeCell ref="B33:B43"/>
-    <mergeCell ref="A44:A75"/>
-    <mergeCell ref="B64:B75"/>
-    <mergeCell ref="B23:B32"/>
-    <mergeCell ref="B44:B53"/>
-    <mergeCell ref="B54:B63"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Methanol/Methanol_DAC_Brownfield_Leuna/Datenbank.xlsx
+++ b/Methanol/Methanol_DAC_Brownfield_Leuna/Datenbank.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Methanol\Methanol_DAC_Brownfield_Leuna\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\Methanol\Methanol_DAC_Brownfield_Leuna\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52B68AD7-D372-408F-9EB1-6562BD3F2D16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6D3C7E0-0F3D-4D08-B799-78944B67A11A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -1332,10 +1332,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="44" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="0.0000"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="0.00000"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="0.00000"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -1497,13 +1497,13 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1512,82 +1512,76 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2164,7 +2158,7 @@
         <v>26</v>
       </c>
       <c r="E4" s="14">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="F4" s="10" t="s">
         <v>83</v>
@@ -4849,7 +4843,7 @@
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="49"/>
+      <c r="A114" s="36"/>
       <c r="B114" s="43"/>
       <c r="C114" s="10" t="s">
         <v>174</v>
@@ -4862,7 +4856,7 @@
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="49"/>
+      <c r="A115" s="36"/>
       <c r="B115" s="47"/>
       <c r="C115" s="18"/>
       <c r="D115" s="18"/>
@@ -4870,7 +4864,7 @@
       <c r="F115" s="18"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="49"/>
+      <c r="A116" s="36"/>
       <c r="B116" s="46" t="s">
         <v>183</v>
       </c>
@@ -4885,7 +4879,7 @@
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="49"/>
+      <c r="A117" s="36"/>
       <c r="B117" s="43"/>
       <c r="C117" s="10" t="s">
         <v>181</v>
@@ -4898,7 +4892,7 @@
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="49"/>
+      <c r="A118" s="36"/>
       <c r="B118" s="43"/>
       <c r="C118" s="10" t="s">
         <v>177</v>
@@ -4911,7 +4905,7 @@
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="49"/>
+      <c r="A119" s="36"/>
       <c r="B119" s="43"/>
       <c r="C119" s="10" t="s">
         <v>179</v>
@@ -4924,7 +4918,7 @@
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="49"/>
+      <c r="A120" s="36"/>
       <c r="B120" s="43"/>
       <c r="C120" s="10" t="s">
         <v>182</v>
@@ -4937,7 +4931,7 @@
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="49"/>
+      <c r="A121" s="36"/>
       <c r="B121" s="43"/>
       <c r="C121" s="10" t="s">
         <v>191</v>
@@ -4950,11 +4944,11 @@
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="49"/>
+      <c r="A122" s="36"/>
       <c r="B122" s="43"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="49"/>
+      <c r="A123" s="36"/>
       <c r="B123" s="46" t="s">
         <v>206</v>
       </c>
@@ -4970,7 +4964,7 @@
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="49"/>
+      <c r="A124" s="36"/>
       <c r="B124" s="43"/>
       <c r="C124" s="10" t="s">
         <v>204</v>
@@ -4983,7 +4977,7 @@
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="49"/>
+      <c r="A125" s="36"/>
       <c r="B125" s="43"/>
       <c r="C125" s="10" t="s">
         <v>215</v>
@@ -4996,7 +4990,7 @@
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="49"/>
+      <c r="A126" s="36"/>
       <c r="B126" s="43"/>
       <c r="C126" s="10" t="s">
         <v>205</v>
@@ -5009,7 +5003,7 @@
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="49"/>
+      <c r="A127" s="36"/>
       <c r="B127" s="43"/>
       <c r="C127" s="10" t="s">
         <v>337</v>
@@ -5022,7 +5016,7 @@
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="49"/>
+      <c r="A128" s="36"/>
       <c r="B128" s="43"/>
       <c r="C128" s="10" t="s">
         <v>361</v>
@@ -5035,7 +5029,7 @@
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="49"/>
+      <c r="A129" s="36"/>
       <c r="B129" s="43"/>
       <c r="C129" s="10" t="s">
         <v>363</v>
@@ -5048,7 +5042,7 @@
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="49"/>
+      <c r="A130" s="36"/>
       <c r="B130" s="43"/>
       <c r="C130" s="10" t="s">
         <v>217</v>
@@ -5061,7 +5055,7 @@
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="49"/>
+      <c r="A131" s="36"/>
       <c r="B131" s="43"/>
       <c r="C131" s="10" t="s">
         <v>221</v>
@@ -5074,7 +5068,7 @@
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="49"/>
+      <c r="A132" s="36"/>
       <c r="B132" s="43"/>
       <c r="C132" s="10" t="s">
         <v>202</v>
@@ -5087,7 +5081,7 @@
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="49"/>
+      <c r="A133" s="36"/>
       <c r="B133" s="43"/>
       <c r="C133" s="10" t="s">
         <v>278</v>
@@ -5100,7 +5094,7 @@
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="49"/>
+      <c r="A134" s="36"/>
       <c r="B134" s="43"/>
       <c r="C134" s="10" t="s">
         <v>281</v>
@@ -5113,11 +5107,11 @@
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="49"/>
+      <c r="A135" s="36"/>
       <c r="B135" s="43"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="49"/>
+      <c r="A136" s="36"/>
       <c r="B136" s="46" t="s">
         <v>222</v>
       </c>
@@ -5133,8 +5127,8 @@
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="49"/>
-      <c r="B137" s="48"/>
+      <c r="A137" s="36"/>
+      <c r="B137" s="43"/>
       <c r="C137" s="10" t="s">
         <v>339</v>
       </c>
@@ -5146,8 +5140,8 @@
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="49"/>
-      <c r="B138" s="48"/>
+      <c r="A138" s="36"/>
+      <c r="B138" s="43"/>
       <c r="C138" s="10" t="s">
         <v>225</v>
       </c>
@@ -5159,8 +5153,8 @@
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="49"/>
-      <c r="B139" s="48"/>
+      <c r="A139" s="36"/>
+      <c r="B139" s="43"/>
       <c r="C139" s="10" t="s">
         <v>282</v>
       </c>
@@ -5172,8 +5166,8 @@
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="49"/>
-      <c r="B140" s="48"/>
+      <c r="A140" s="36"/>
+      <c r="B140" s="43"/>
       <c r="C140" s="10" t="s">
         <v>284</v>
       </c>
@@ -5185,11 +5179,11 @@
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="49"/>
+      <c r="A141" s="36"/>
       <c r="B141" s="47"/>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="49"/>
+      <c r="A142" s="36"/>
       <c r="B142" s="46" t="s">
         <v>367</v>
       </c>
@@ -5205,7 +5199,7 @@
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="49"/>
+      <c r="A143" s="36"/>
       <c r="B143" s="43"/>
       <c r="C143" s="10" t="s">
         <v>370</v>
@@ -5218,19 +5212,10 @@
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144" s="49"/>
+      <c r="A144" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A2:A43"/>
-    <mergeCell ref="B2:B11"/>
-    <mergeCell ref="B12:B22"/>
-    <mergeCell ref="B33:B43"/>
-    <mergeCell ref="A44:A75"/>
-    <mergeCell ref="B64:B75"/>
-    <mergeCell ref="B23:B32"/>
-    <mergeCell ref="B44:B53"/>
-    <mergeCell ref="B54:B63"/>
     <mergeCell ref="B142:B143"/>
     <mergeCell ref="B136:B141"/>
     <mergeCell ref="A113:A144"/>
@@ -5246,6 +5231,15 @@
     <mergeCell ref="B107:B109"/>
     <mergeCell ref="B99:B102"/>
     <mergeCell ref="B103:B106"/>
+    <mergeCell ref="A2:A43"/>
+    <mergeCell ref="B2:B11"/>
+    <mergeCell ref="B12:B22"/>
+    <mergeCell ref="B33:B43"/>
+    <mergeCell ref="A44:A75"/>
+    <mergeCell ref="B64:B75"/>
+    <mergeCell ref="B23:B32"/>
+    <mergeCell ref="B44:B53"/>
+    <mergeCell ref="B54:B63"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Methanol/Methanol_DAC_Brownfield_Leuna/Datenbank.xlsx
+++ b/Methanol/Methanol_DAC_Brownfield_Leuna/Datenbank.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\Methanol\Methanol_DAC_Brownfield_Leuna\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Methanol\Methanol_DAC_Brownfield_Leuna\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6D3C7E0-0F3D-4D08-B799-78944B67A11A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56FC0D4C-BAE2-4676-8A5D-3AC8950F0936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -198,7 +198,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="371">
   <si>
     <t>PEM Elektrolyse</t>
   </si>
@@ -883,12 +883,6 @@
     <t>calc_cost_h2</t>
   </si>
   <si>
-    <t>calc_einnahmen_stromverkauf_schattenvariable</t>
-  </si>
-  <si>
-    <t>Schattenvariable Einnahmen Stromverkauf</t>
-  </si>
-  <si>
     <t>CO2-Bereitstellung / Direct Air Capture</t>
   </si>
   <si>
@@ -1195,13 +1189,7 @@
     <t>result_qverkauf_flowsum</t>
   </si>
   <si>
-    <t>calc_einnahmen_qverkauf_schattenvariable</t>
-  </si>
-  <si>
     <t>calc_einnnahmen_qverkauf</t>
-  </si>
-  <si>
-    <t>Schattenvariable Einnahmen Wärmeverkauf</t>
   </si>
   <si>
     <t>Einnahmen aus Wärmeverkauf</t>
@@ -1332,10 +1320,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
-    <numFmt numFmtId="167" formatCode="0.00000"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.00000"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -1497,13 +1485,13 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1514,36 +1502,36 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2215,19 +2203,19 @@
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="36"/>
       <c r="B8" s="46" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C8" s="20" t="s">
         <v>84</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E8" s="25">
         <v>1.5</v>
       </c>
       <c r="F8" s="20" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -2237,7 +2225,7 @@
         <v>85</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E9" s="13">
         <v>285.39999999999998</v>
@@ -2253,13 +2241,13 @@
         <v>10</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E10" s="13">
         <v>5110</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -2269,7 +2257,7 @@
         <v>11</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E11" s="15">
         <v>0.05</v>
@@ -2285,29 +2273,29 @@
         <v>86</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E12" s="13">
         <v>0.189</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="36"/>
       <c r="B13" s="43"/>
       <c r="C13" s="10" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E13" s="13">
         <v>1.375</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -2317,7 +2305,7 @@
         <v>13</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E14" s="16">
         <v>25</v>
@@ -2333,7 +2321,7 @@
         <v>15</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E15" s="19">
         <v>0.08</v>
@@ -2345,13 +2333,13 @@
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="36"/>
       <c r="B16" s="46" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C16" s="20" t="s">
         <v>8</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E16" s="21">
         <v>3.7</v>
@@ -2367,13 +2355,13 @@
         <v>84</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E17" s="15">
         <v>0.27</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -2383,13 +2371,13 @@
         <v>10</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E18" s="15">
         <v>700</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -2399,7 +2387,7 @@
         <v>11</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E19" s="15">
         <v>0.02</v>
@@ -2415,7 +2403,7 @@
         <v>13</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E20" s="15">
         <v>20</v>
@@ -2431,7 +2419,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E21" s="19">
         <v>0.05</v>
@@ -2443,35 +2431,35 @@
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="36"/>
       <c r="B22" s="39" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>84</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E22" s="13">
         <v>0.5</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="36"/>
       <c r="B23" s="39"/>
       <c r="C23" s="10" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E23" s="13">
         <v>1.75</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -2481,13 +2469,13 @@
         <v>10</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E24" s="13">
         <v>7000</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -2497,7 +2485,7 @@
         <v>11</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E25" s="15">
         <v>0.05</v>
@@ -2513,7 +2501,7 @@
         <v>13</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E26" s="16">
         <v>15</v>
@@ -2529,7 +2517,7 @@
         <v>15</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E27" s="15">
         <v>7.0000000000000007E-2</v>
@@ -2673,19 +2661,19 @@
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="36"/>
       <c r="B36" s="41" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C36" s="11" t="s">
         <v>87</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="E36" s="17">
         <v>2.83</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -2695,7 +2683,7 @@
         <v>11</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="E37" s="15">
         <v>0.03</v>
@@ -2711,7 +2699,7 @@
         <v>13</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="E38" s="16">
         <v>30</v>
@@ -2727,7 +2715,7 @@
         <v>20</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="E39" s="15">
         <v>7.3999999999999999E-4</v>
@@ -2743,7 +2731,7 @@
         <v>35</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="E40" s="15">
         <v>0.98</v>
@@ -2759,7 +2747,7 @@
         <v>36</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="E41" s="15">
         <v>0.98</v>
@@ -2775,7 +2763,7 @@
         <v>15</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="E42" s="15">
         <v>0.05</v>
@@ -2791,7 +2779,7 @@
         <v>88</v>
       </c>
       <c r="D43" s="18" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="E43" s="19">
         <v>0</v>
@@ -3225,7 +3213,7 @@
         <v>78</v>
       </c>
       <c r="E69" s="31">
-        <v>-1E-4</v>
+        <v>0</v>
       </c>
       <c r="F69" s="30" t="s">
         <v>19</v>
@@ -3234,19 +3222,19 @@
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="36"/>
       <c r="B70" s="26" t="s">
+        <v>322</v>
+      </c>
+      <c r="C70" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="D70" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="C70" s="10" t="s">
-        <v>325</v>
-      </c>
-      <c r="D70" s="10" t="s">
-        <v>326</v>
-      </c>
       <c r="E70" s="15">
-        <v>-1E-4</v>
+        <v>0</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
@@ -3270,19 +3258,19 @@
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="37"/>
       <c r="B72" s="8" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C72" s="22" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D72" s="22" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E72" s="23">
         <v>-0.6</v>
       </c>
       <c r="F72" s="22" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
   </sheetData>
@@ -3309,7 +3297,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83AB2E79-6F94-41B5-A552-C40EC4890194}">
-  <dimension ref="A1:F144"/>
+  <dimension ref="A1:F142"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" style="10" customWidth="1"/>
@@ -3479,13 +3467,13 @@
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="36"/>
       <c r="B12" s="46" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C12" s="20" t="s">
         <v>96</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E12" s="25"/>
       <c r="F12" s="20" t="s">
@@ -3496,14 +3484,14 @@
       <c r="A13" s="36"/>
       <c r="B13" s="43"/>
       <c r="C13" s="10" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E13" s="13"/>
       <c r="F13" s="10" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -3513,7 +3501,7 @@
         <v>139</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E14" s="13"/>
       <c r="F14" s="13" t="s">
@@ -3524,14 +3512,14 @@
       <c r="A15" s="36"/>
       <c r="B15" s="43"/>
       <c r="C15" s="10" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E15" s="15"/>
       <c r="F15" s="10" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -3541,7 +3529,7 @@
         <v>84</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E16" s="13"/>
       <c r="F16" s="10" t="s">
@@ -3555,7 +3543,7 @@
         <v>141</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E17" s="13"/>
       <c r="F17" s="10" t="s">
@@ -3569,7 +3557,7 @@
         <v>155</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E18" s="16"/>
       <c r="F18" s="10" t="s">
@@ -3583,7 +3571,7 @@
         <v>196</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E19" s="16"/>
       <c r="F19" s="10" t="s">
@@ -3597,7 +3585,7 @@
         <v>167</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E20" s="16"/>
       <c r="F20" s="10" t="s">
@@ -3611,7 +3599,7 @@
         <v>188</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E21" s="16"/>
       <c r="F21" s="10" t="s">
@@ -3629,17 +3617,17 @@
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="36"/>
       <c r="B23" s="46" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C23" s="10" t="s">
         <v>96</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E23" s="13"/>
       <c r="F23" s="10" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -3649,7 +3637,7 @@
         <v>107</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E24" s="13"/>
       <c r="F24" s="10" t="s">
@@ -3663,25 +3651,25 @@
         <v>84</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E25" s="15"/>
       <c r="F25" s="10" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="36"/>
       <c r="B26" s="43"/>
       <c r="C26" s="10" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E26" s="16"/>
       <c r="F26" s="10" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -3691,7 +3679,7 @@
         <v>141</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E27" s="16"/>
       <c r="F27" s="10" t="s">
@@ -3705,7 +3693,7 @@
         <v>155</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E28" s="16"/>
       <c r="F28" s="10" t="s">
@@ -3719,7 +3707,7 @@
         <v>196</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E29" s="16"/>
       <c r="F29" s="10" t="s">
@@ -3733,7 +3721,7 @@
         <v>167</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E30" s="15"/>
       <c r="F30" s="10" t="s">
@@ -3747,7 +3735,7 @@
         <v>188</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E31" s="15"/>
       <c r="F31" s="10" t="s">
@@ -3765,13 +3753,13 @@
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="36"/>
       <c r="B33" s="39" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C33" s="10" t="s">
         <v>96</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E33" s="13"/>
       <c r="F33" s="10" t="s">
@@ -3785,7 +3773,7 @@
         <v>107</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E34" s="13"/>
       <c r="F34" s="10" t="s">
@@ -3799,7 +3787,7 @@
         <v>84</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E35" s="15"/>
       <c r="F35" s="10" t="s">
@@ -3810,28 +3798,28 @@
       <c r="A36" s="36"/>
       <c r="B36" s="39"/>
       <c r="C36" s="10" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E36" s="15"/>
       <c r="F36" s="10" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="36"/>
       <c r="B37" s="39"/>
       <c r="C37" s="10" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E37" s="16"/>
       <c r="F37" s="10" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
@@ -3841,7 +3829,7 @@
         <v>141</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E38" s="16"/>
       <c r="F38" s="10" t="s">
@@ -3855,7 +3843,7 @@
         <v>155</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E39" s="16"/>
       <c r="F39" s="10" t="s">
@@ -3869,7 +3857,7 @@
         <v>196</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E40" s="16"/>
       <c r="F40" s="10" t="s">
@@ -3883,7 +3871,7 @@
         <v>167</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E41" s="15"/>
       <c r="F41" s="10" t="s">
@@ -3897,7 +3885,7 @@
         <v>188</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E42" s="15"/>
       <c r="F42" s="10" t="s">
@@ -3924,7 +3912,7 @@
       </c>
       <c r="E44" s="17"/>
       <c r="F44" s="11" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -3938,7 +3926,7 @@
       </c>
       <c r="E45" s="15"/>
       <c r="F45" s="10" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -4050,17 +4038,17 @@
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="36"/>
       <c r="B54" s="39" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C54" s="10" t="s">
         <v>113</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="E54" s="13"/>
       <c r="F54" s="10" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
@@ -4070,11 +4058,11 @@
         <v>111</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="E55" s="15"/>
       <c r="F55" s="10" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
@@ -4084,11 +4072,11 @@
         <v>135</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="E56" s="16"/>
       <c r="F56" s="10" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
@@ -4098,11 +4086,11 @@
         <v>136</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="E57" s="15"/>
       <c r="F57" s="10" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
@@ -4112,7 +4100,7 @@
         <v>141</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="E58" s="15"/>
       <c r="F58" s="10" t="s">
@@ -4126,7 +4114,7 @@
         <v>155</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="E59" s="15"/>
       <c r="F59" s="10" t="s">
@@ -4140,7 +4128,7 @@
         <v>196</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="E60" s="15"/>
       <c r="F60" s="10" t="s">
@@ -4154,7 +4142,7 @@
         <v>167</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="E61" s="15"/>
       <c r="F61" s="10" t="s">
@@ -4168,7 +4156,7 @@
         <v>188</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="E62" s="15"/>
       <c r="F62" s="10" t="s">
@@ -4667,10 +4655,10 @@
       <c r="A100" s="36"/>
       <c r="B100" s="43"/>
       <c r="C100" s="10" t="s">
-        <v>228</v>
+        <v>150</v>
       </c>
       <c r="D100" s="10" t="s">
-        <v>227</v>
+        <v>147</v>
       </c>
       <c r="E100" s="15"/>
       <c r="F100" s="10" t="s">
@@ -4679,200 +4667,198 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="36"/>
-      <c r="B101" s="43"/>
-      <c r="C101" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="D101" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="E101" s="15"/>
-      <c r="F101" s="10" t="s">
-        <v>149</v>
-      </c>
+      <c r="B101" s="47"/>
+      <c r="C101" s="18"/>
+      <c r="D101" s="18"/>
+      <c r="E101" s="19"/>
+      <c r="F101" s="18"/>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="36"/>
-      <c r="B102" s="47"/>
-      <c r="C102" s="18"/>
-      <c r="D102" s="18"/>
-      <c r="E102" s="19"/>
-      <c r="F102" s="18"/>
+      <c r="B102" s="46" t="s">
+        <v>326</v>
+      </c>
+      <c r="C102" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="D102" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="E102" s="15"/>
+      <c r="F102" s="10" t="s">
+        <v>315</v>
+      </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="36"/>
-      <c r="B103" s="46" t="s">
-        <v>328</v>
-      </c>
+      <c r="B103" s="43"/>
       <c r="C103" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="D103" s="10" t="s">
         <v>329</v>
-      </c>
-      <c r="D103" s="10" t="s">
-        <v>330</v>
       </c>
       <c r="E103" s="15"/>
       <c r="F103" s="10" t="s">
-        <v>317</v>
+        <v>149</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="36"/>
-      <c r="B104" s="43"/>
-      <c r="C104" s="10" t="s">
-        <v>333</v>
-      </c>
-      <c r="D104" s="10" t="s">
-        <v>331</v>
-      </c>
+      <c r="B104" s="47"/>
       <c r="E104" s="15"/>
-      <c r="F104" s="10" t="s">
-        <v>149</v>
-      </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="36"/>
-      <c r="B105" s="43"/>
-      <c r="C105" s="10" t="s">
-        <v>334</v>
-      </c>
-      <c r="D105" s="10" t="s">
-        <v>332</v>
-      </c>
-      <c r="E105" s="15"/>
-      <c r="F105" s="10" t="s">
-        <v>149</v>
+      <c r="B105" s="46" t="s">
+        <v>79</v>
+      </c>
+      <c r="C105" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="D105" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="E105" s="21"/>
+      <c r="F105" s="20" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="36"/>
-      <c r="B106" s="47"/>
+      <c r="B106" s="43"/>
+      <c r="C106" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="D106" s="10" t="s">
+        <v>148</v>
+      </c>
       <c r="E106" s="15"/>
+      <c r="F106" s="10" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="36"/>
-      <c r="B107" s="46" t="s">
-        <v>79</v>
-      </c>
-      <c r="C107" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="D107" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="E107" s="21"/>
-      <c r="F107" s="20" t="s">
-        <v>132</v>
-      </c>
+      <c r="B107" s="47"/>
+      <c r="C107" s="18"/>
+      <c r="D107" s="18"/>
+      <c r="E107" s="19"/>
+      <c r="F107" s="18"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="36"/>
-      <c r="B108" s="43"/>
+      <c r="B108" s="46" t="s">
+        <v>272</v>
+      </c>
       <c r="C108" s="10" t="s">
-        <v>151</v>
+        <v>271</v>
       </c>
       <c r="D108" s="10" t="s">
-        <v>148</v>
+        <v>274</v>
       </c>
       <c r="E108" s="15"/>
       <c r="F108" s="10" t="s">
-        <v>149</v>
+        <v>260</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="36"/>
-      <c r="B109" s="47"/>
-      <c r="C109" s="18"/>
-      <c r="D109" s="18"/>
-      <c r="E109" s="19"/>
-      <c r="F109" s="18"/>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="36"/>
-      <c r="B110" s="46" t="s">
-        <v>274</v>
-      </c>
-      <c r="C110" s="10" t="s">
+      <c r="B109" s="43"/>
+      <c r="C109" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="D110" s="10" t="s">
-        <v>276</v>
-      </c>
-      <c r="E110" s="15"/>
-      <c r="F110" s="10" t="s">
-        <v>262</v>
-      </c>
+      <c r="D109" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="E109" s="15"/>
+      <c r="F109" s="10" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A110" s="37"/>
+      <c r="B110" s="44"/>
+      <c r="C110" s="22"/>
+      <c r="D110" s="22"/>
+      <c r="E110" s="23"/>
+      <c r="F110" s="22"/>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="36"/>
-      <c r="B111" s="43"/>
-      <c r="C111" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="D111" s="10" t="s">
-        <v>277</v>
-      </c>
-      <c r="E111" s="15"/>
-      <c r="F111" s="10" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="37"/>
-      <c r="B112" s="44"/>
-      <c r="C112" s="22"/>
-      <c r="D112" s="22"/>
-      <c r="E112" s="23"/>
-      <c r="F112" s="22"/>
+      <c r="A111" s="35" t="s">
+        <v>163</v>
+      </c>
+      <c r="B111" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="C111" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="D111" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="E111" s="11"/>
+      <c r="F111" s="11" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A112" s="36"/>
+      <c r="B112" s="43"/>
+      <c r="C112" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="D112" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="F112" s="10" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="35" t="s">
-        <v>163</v>
-      </c>
-      <c r="B113" s="45" t="s">
-        <v>13</v>
-      </c>
-      <c r="C113" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="D113" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="E113" s="11"/>
-      <c r="F113" s="11" t="s">
-        <v>140</v>
-      </c>
+      <c r="A113" s="36"/>
+      <c r="B113" s="47"/>
+      <c r="C113" s="18"/>
+      <c r="D113" s="18"/>
+      <c r="E113" s="18"/>
+      <c r="F113" s="18"/>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" s="36"/>
-      <c r="B114" s="43"/>
+      <c r="B114" s="46" t="s">
+        <v>183</v>
+      </c>
       <c r="C114" s="10" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="D114" s="10" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="F114" s="10" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" s="36"/>
-      <c r="B115" s="47"/>
-      <c r="C115" s="18"/>
-      <c r="D115" s="18"/>
-      <c r="E115" s="18"/>
-      <c r="F115" s="18"/>
+      <c r="B115" s="43"/>
+      <c r="C115" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D115" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="F115" s="10" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" s="36"/>
-      <c r="B116" s="46" t="s">
-        <v>183</v>
-      </c>
+      <c r="B116" s="43"/>
       <c r="C116" s="10" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="D116" s="10" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="F116" s="10" t="s">
         <v>149</v>
@@ -4882,10 +4868,10 @@
       <c r="A117" s="36"/>
       <c r="B117" s="43"/>
       <c r="C117" s="10" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D117" s="10" t="s">
-        <v>336</v>
+        <v>178</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>149</v>
@@ -4895,10 +4881,10 @@
       <c r="A118" s="36"/>
       <c r="B118" s="43"/>
       <c r="C118" s="10" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="D118" s="10" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F118" s="10" t="s">
         <v>149</v>
@@ -4908,10 +4894,10 @@
       <c r="A119" s="36"/>
       <c r="B119" s="43"/>
       <c r="C119" s="10" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="D119" s="10" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>149</v>
@@ -4920,57 +4906,57 @@
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" s="36"/>
       <c r="B120" s="43"/>
-      <c r="C120" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="D120" s="10" t="s">
-        <v>180</v>
-      </c>
-      <c r="F120" s="10" t="s">
-        <v>149</v>
-      </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" s="36"/>
-      <c r="B121" s="43"/>
-      <c r="C121" s="10" t="s">
-        <v>191</v>
-      </c>
-      <c r="D121" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="F121" s="10" t="s">
-        <v>149</v>
+      <c r="B121" s="46" t="s">
+        <v>206</v>
+      </c>
+      <c r="C121" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="D121" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="E121" s="20"/>
+      <c r="F121" s="20" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" s="36"/>
       <c r="B122" s="43"/>
+      <c r="C122" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="D122" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="F122" s="10" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" s="36"/>
-      <c r="B123" s="46" t="s">
-        <v>206</v>
-      </c>
-      <c r="C123" s="20" t="s">
-        <v>203</v>
-      </c>
-      <c r="D123" s="20" t="s">
-        <v>207</v>
-      </c>
-      <c r="E123" s="20"/>
-      <c r="F123" s="20" t="s">
-        <v>208</v>
+      <c r="B123" s="43"/>
+      <c r="C123" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="D123" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="F123" s="10" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" s="36"/>
       <c r="B124" s="43"/>
       <c r="C124" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D124" s="10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F124" s="10" t="s">
         <v>208</v>
@@ -4980,88 +4966,88 @@
       <c r="A125" s="36"/>
       <c r="B125" s="43"/>
       <c r="C125" s="10" t="s">
-        <v>215</v>
+        <v>333</v>
       </c>
       <c r="D125" s="10" t="s">
-        <v>214</v>
+        <v>334</v>
       </c>
       <c r="F125" s="10" t="s">
-        <v>219</v>
+        <v>337</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" s="36"/>
       <c r="B126" s="43"/>
       <c r="C126" s="10" t="s">
-        <v>205</v>
+        <v>357</v>
       </c>
       <c r="D126" s="10" t="s">
-        <v>209</v>
+        <v>358</v>
       </c>
       <c r="F126" s="10" t="s">
-        <v>208</v>
+        <v>337</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" s="36"/>
       <c r="B127" s="43"/>
       <c r="C127" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="D127" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="F127" s="10" t="s">
         <v>337</v>
-      </c>
-      <c r="D127" s="10" t="s">
-        <v>338</v>
-      </c>
-      <c r="F127" s="10" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" s="36"/>
       <c r="B128" s="43"/>
       <c r="C128" s="10" t="s">
-        <v>361</v>
+        <v>217</v>
       </c>
       <c r="D128" s="10" t="s">
-        <v>362</v>
+        <v>216</v>
       </c>
       <c r="F128" s="10" t="s">
-        <v>341</v>
+        <v>218</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" s="36"/>
       <c r="B129" s="43"/>
       <c r="C129" s="10" t="s">
-        <v>363</v>
+        <v>221</v>
       </c>
       <c r="D129" s="10" t="s">
-        <v>364</v>
+        <v>211</v>
       </c>
       <c r="F129" s="10" t="s">
-        <v>341</v>
+        <v>212</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" s="36"/>
       <c r="B130" s="43"/>
       <c r="C130" s="10" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="D130" s="10" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="F130" s="10" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" s="36"/>
       <c r="B131" s="43"/>
       <c r="C131" s="10" t="s">
-        <v>221</v>
+        <v>276</v>
       </c>
       <c r="D131" s="10" t="s">
-        <v>211</v>
+        <v>277</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>212</v>
@@ -5071,166 +5057,125 @@
       <c r="A132" s="36"/>
       <c r="B132" s="43"/>
       <c r="C132" s="10" t="s">
-        <v>202</v>
+        <v>279</v>
       </c>
       <c r="D132" s="10" t="s">
-        <v>220</v>
+        <v>278</v>
       </c>
       <c r="F132" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" s="36"/>
       <c r="B133" s="43"/>
-      <c r="C133" s="10" t="s">
-        <v>278</v>
-      </c>
-      <c r="D133" s="10" t="s">
-        <v>279</v>
-      </c>
-      <c r="F133" s="10" t="s">
-        <v>212</v>
-      </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" s="36"/>
-      <c r="B134" s="43"/>
-      <c r="C134" s="10" t="s">
-        <v>281</v>
-      </c>
-      <c r="D134" s="10" t="s">
-        <v>280</v>
-      </c>
-      <c r="F134" s="10" t="s">
-        <v>213</v>
+      <c r="B134" s="46" t="s">
+        <v>222</v>
+      </c>
+      <c r="C134" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="D134" s="20" t="s">
+        <v>223</v>
+      </c>
+      <c r="E134" s="20"/>
+      <c r="F134" s="20" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" s="36"/>
       <c r="B135" s="43"/>
+      <c r="C135" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="D135" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="F135" s="10" t="s">
+        <v>337</v>
+      </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" s="36"/>
-      <c r="B136" s="46" t="s">
-        <v>222</v>
-      </c>
-      <c r="C136" s="20" t="s">
-        <v>224</v>
-      </c>
-      <c r="D136" s="20" t="s">
-        <v>223</v>
-      </c>
-      <c r="E136" s="20"/>
-      <c r="F136" s="20" t="s">
-        <v>208</v>
+      <c r="B136" s="43"/>
+      <c r="C136" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="D136" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="F136" s="10" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" s="36"/>
       <c r="B137" s="43"/>
       <c r="C137" s="10" t="s">
-        <v>339</v>
+        <v>280</v>
       </c>
       <c r="D137" s="10" t="s">
-        <v>340</v>
+        <v>281</v>
       </c>
       <c r="F137" s="10" t="s">
-        <v>341</v>
+        <v>212</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" s="36"/>
       <c r="B138" s="43"/>
       <c r="C138" s="10" t="s">
-        <v>225</v>
+        <v>282</v>
       </c>
       <c r="D138" s="10" t="s">
-        <v>226</v>
+        <v>331</v>
       </c>
       <c r="F138" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" s="36"/>
-      <c r="B139" s="43"/>
-      <c r="C139" s="10" t="s">
-        <v>282</v>
-      </c>
-      <c r="D139" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="F139" s="10" t="s">
-        <v>212</v>
-      </c>
+      <c r="B139" s="47"/>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" s="36"/>
-      <c r="B140" s="43"/>
-      <c r="C140" s="10" t="s">
-        <v>284</v>
-      </c>
-      <c r="D140" s="10" t="s">
-        <v>335</v>
-      </c>
-      <c r="F140" s="10" t="s">
-        <v>213</v>
+      <c r="B140" s="46" t="s">
+        <v>363</v>
+      </c>
+      <c r="C140" s="20" t="s">
+        <v>364</v>
+      </c>
+      <c r="D140" s="20" t="s">
+        <v>365</v>
+      </c>
+      <c r="E140" s="20"/>
+      <c r="F140" s="20" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" s="36"/>
-      <c r="B141" s="47"/>
+      <c r="B141" s="43"/>
+      <c r="C141" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="D141" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="F141" s="10" t="s">
+        <v>295</v>
+      </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" s="36"/>
-      <c r="B142" s="46" t="s">
-        <v>367</v>
-      </c>
-      <c r="C142" s="20" t="s">
-        <v>368</v>
-      </c>
-      <c r="D142" s="20" t="s">
-        <v>369</v>
-      </c>
-      <c r="E142" s="20"/>
-      <c r="F142" s="20" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="36"/>
-      <c r="B143" s="43"/>
-      <c r="C143" s="10" t="s">
-        <v>370</v>
-      </c>
-      <c r="D143" s="10" t="s">
-        <v>371</v>
-      </c>
-      <c r="F143" s="10" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="B142:B143"/>
-    <mergeCell ref="B136:B141"/>
-    <mergeCell ref="A113:A144"/>
-    <mergeCell ref="B110:B112"/>
-    <mergeCell ref="B76:B78"/>
-    <mergeCell ref="B116:B122"/>
-    <mergeCell ref="B123:B135"/>
-    <mergeCell ref="B113:B115"/>
-    <mergeCell ref="A76:A98"/>
-    <mergeCell ref="B79:B88"/>
-    <mergeCell ref="B89:B98"/>
-    <mergeCell ref="A99:A112"/>
-    <mergeCell ref="B107:B109"/>
-    <mergeCell ref="B99:B102"/>
-    <mergeCell ref="B103:B106"/>
     <mergeCell ref="A2:A43"/>
     <mergeCell ref="B2:B11"/>
     <mergeCell ref="B12:B22"/>
@@ -5240,6 +5185,21 @@
     <mergeCell ref="B23:B32"/>
     <mergeCell ref="B44:B53"/>
     <mergeCell ref="B54:B63"/>
+    <mergeCell ref="B140:B141"/>
+    <mergeCell ref="B134:B139"/>
+    <mergeCell ref="A111:A142"/>
+    <mergeCell ref="B108:B110"/>
+    <mergeCell ref="B76:B78"/>
+    <mergeCell ref="B114:B120"/>
+    <mergeCell ref="B121:B133"/>
+    <mergeCell ref="B111:B113"/>
+    <mergeCell ref="A76:A98"/>
+    <mergeCell ref="B79:B88"/>
+    <mergeCell ref="B89:B98"/>
+    <mergeCell ref="A99:A110"/>
+    <mergeCell ref="B105:B107"/>
+    <mergeCell ref="B99:B101"/>
+    <mergeCell ref="B102:B104"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5256,47 +5216,47 @@
   <sheetData>
     <row r="1" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B1" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="22" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B22" s="6" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B24" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B26" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B27" s="3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B28" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="30" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B30" s="5" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="31" spans="2:2" x14ac:dyDescent="0.3">
